--- a/Configs/GameConfig/Datas/HeroGrowthConfig.xlsx
+++ b/Configs/GameConfig/Datas/HeroGrowthConfig.xlsx
@@ -636,13 +636,13 @@
         <v>50</v>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -689,16 +689,16 @@
         <v>130</v>
       </c>
       <c r="E5" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -745,16 +745,16 @@
         <v>180</v>
       </c>
       <c r="E6" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F6" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G6" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -801,16 +801,16 @@
         <v>230</v>
       </c>
       <c r="E7" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="F7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G7" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H7" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -857,16 +857,16 @@
         <v>280</v>
       </c>
       <c r="E8" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="F8" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G8" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H8" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -913,16 +913,16 @@
         <v>330</v>
       </c>
       <c r="E9" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="F9" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="G9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -969,16 +969,16 @@
         <v>380</v>
       </c>
       <c r="E10" t="n">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="F10" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1025,16 +1025,16 @@
         <v>430</v>
       </c>
       <c r="E11" t="n">
-        <v>155</v>
+        <v>190</v>
       </c>
       <c r="F11" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="G11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1081,10 +1081,10 @@
         <v>480</v>
       </c>
       <c r="E12" t="n">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="F12" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G12" t="n">
         <v>18</v>
@@ -1137,16 +1137,16 @@
         <v>530</v>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>230</v>
       </c>
       <c r="F13" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="G13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1193,16 +1193,16 @@
         <v>580</v>
       </c>
       <c r="E14" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="F14" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="G14" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H14" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1249,16 +1249,16 @@
         <v>630</v>
       </c>
       <c r="E15" t="n">
-        <v>215</v>
+        <v>270</v>
       </c>
       <c r="F15" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="G15" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H15" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1305,16 +1305,16 @@
         <v>680</v>
       </c>
       <c r="E16" t="n">
-        <v>230</v>
+        <v>290</v>
       </c>
       <c r="F16" t="n">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="G16" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H16" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1361,16 +1361,16 @@
         <v>730</v>
       </c>
       <c r="E17" t="n">
-        <v>245</v>
+        <v>310</v>
       </c>
       <c r="F17" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="G17" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H17" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1417,16 +1417,16 @@
         <v>780</v>
       </c>
       <c r="E18" t="n">
-        <v>260</v>
+        <v>330</v>
       </c>
       <c r="F18" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="G18" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H18" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1473,16 +1473,16 @@
         <v>830</v>
       </c>
       <c r="E19" t="n">
-        <v>275</v>
+        <v>350</v>
       </c>
       <c r="F19" t="n">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="G19" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="H19" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1529,16 +1529,16 @@
         <v>880</v>
       </c>
       <c r="E20" t="n">
-        <v>290</v>
+        <v>370</v>
       </c>
       <c r="F20" t="n">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="G20" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="H20" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -1585,16 +1585,16 @@
         <v>930</v>
       </c>
       <c r="E21" t="n">
-        <v>305</v>
+        <v>390</v>
       </c>
       <c r="F21" t="n">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="G21" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="H21" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -1641,16 +1641,16 @@
         <v>980</v>
       </c>
       <c r="E22" t="n">
-        <v>320</v>
+        <v>410</v>
       </c>
       <c r="F22" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G22" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="H22" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -1697,16 +1697,16 @@
         <v>1030</v>
       </c>
       <c r="E23" t="n">
-        <v>335</v>
+        <v>430</v>
       </c>
       <c r="F23" t="n">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="G23" t="n">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="H23" t="n">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -1753,16 +1753,16 @@
         <v>1080</v>
       </c>
       <c r="E24" t="n">
-        <v>350</v>
+        <v>450</v>
       </c>
       <c r="F24" t="n">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="G24" t="n">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="H24" t="n">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -1809,16 +1809,16 @@
         <v>1130</v>
       </c>
       <c r="E25" t="n">
-        <v>365</v>
+        <v>470</v>
       </c>
       <c r="F25" t="n">
-        <v>92</v>
+        <v>115</v>
       </c>
       <c r="G25" t="n">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="H25" t="n">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -1865,16 +1865,16 @@
         <v>1180</v>
       </c>
       <c r="E26" t="n">
-        <v>380</v>
+        <v>490</v>
       </c>
       <c r="F26" t="n">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="G26" t="n">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="H26" t="n">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -1921,16 +1921,16 @@
         <v>1230</v>
       </c>
       <c r="E27" t="n">
-        <v>395</v>
+        <v>510</v>
       </c>
       <c r="F27" t="n">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="G27" t="n">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="H27" t="n">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -1977,16 +1977,16 @@
         <v>1280</v>
       </c>
       <c r="E28" t="n">
-        <v>410</v>
+        <v>530</v>
       </c>
       <c r="F28" t="n">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="G28" t="n">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="H28" t="n">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -2033,16 +2033,16 @@
         <v>1330</v>
       </c>
       <c r="E29" t="n">
-        <v>425</v>
+        <v>550</v>
       </c>
       <c r="F29" t="n">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="G29" t="n">
-        <v>35</v>
+        <v>88</v>
       </c>
       <c r="H29" t="n">
-        <v>35</v>
+        <v>88</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2089,16 +2089,16 @@
         <v>1380</v>
       </c>
       <c r="E30" t="n">
-        <v>440</v>
+        <v>570</v>
       </c>
       <c r="F30" t="n">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="G30" t="n">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="H30" t="n">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2145,16 +2145,16 @@
         <v>1430</v>
       </c>
       <c r="E31" t="n">
-        <v>455</v>
+        <v>590</v>
       </c>
       <c r="F31" t="n">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="G31" t="n">
-        <v>37</v>
+        <v>98</v>
       </c>
       <c r="H31" t="n">
-        <v>37</v>
+        <v>98</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -2201,16 +2201,16 @@
         <v>1480</v>
       </c>
       <c r="E32" t="n">
-        <v>470</v>
+        <v>610</v>
       </c>
       <c r="F32" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="G32" t="n">
-        <v>38</v>
+        <v>103</v>
       </c>
       <c r="H32" t="n">
-        <v>38</v>
+        <v>103</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -2257,16 +2257,16 @@
         <v>1530</v>
       </c>
       <c r="E33" t="n">
-        <v>485</v>
+        <v>630</v>
       </c>
       <c r="F33" t="n">
-        <v>124</v>
+        <v>155</v>
       </c>
       <c r="G33" t="n">
-        <v>39</v>
+        <v>108</v>
       </c>
       <c r="H33" t="n">
-        <v>39</v>
+        <v>108</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -2313,16 +2313,16 @@
         <v>1580</v>
       </c>
       <c r="E34" t="n">
-        <v>500</v>
+        <v>650</v>
       </c>
       <c r="F34" t="n">
-        <v>128</v>
+        <v>160</v>
       </c>
       <c r="G34" t="n">
-        <v>40</v>
+        <v>113</v>
       </c>
       <c r="H34" t="n">
-        <v>40</v>
+        <v>113</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -2369,16 +2369,16 @@
         <v>1630</v>
       </c>
       <c r="E35" t="n">
-        <v>515</v>
+        <v>670</v>
       </c>
       <c r="F35" t="n">
-        <v>132</v>
+        <v>165</v>
       </c>
       <c r="G35" t="n">
-        <v>41</v>
+        <v>118</v>
       </c>
       <c r="H35" t="n">
-        <v>41</v>
+        <v>118</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -2425,16 +2425,16 @@
         <v>1680</v>
       </c>
       <c r="E36" t="n">
-        <v>530</v>
+        <v>690</v>
       </c>
       <c r="F36" t="n">
-        <v>136</v>
+        <v>170</v>
       </c>
       <c r="G36" t="n">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="H36" t="n">
-        <v>42</v>
+        <v>123</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -2481,16 +2481,16 @@
         <v>1730</v>
       </c>
       <c r="E37" t="n">
-        <v>545</v>
+        <v>710</v>
       </c>
       <c r="F37" t="n">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="G37" t="n">
-        <v>43</v>
+        <v>128</v>
       </c>
       <c r="H37" t="n">
-        <v>43</v>
+        <v>128</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -2537,16 +2537,16 @@
         <v>1780</v>
       </c>
       <c r="E38" t="n">
-        <v>560</v>
+        <v>730</v>
       </c>
       <c r="F38" t="n">
-        <v>144</v>
+        <v>180</v>
       </c>
       <c r="G38" t="n">
-        <v>44</v>
+        <v>133</v>
       </c>
       <c r="H38" t="n">
-        <v>44</v>
+        <v>133</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -2593,16 +2593,16 @@
         <v>1830</v>
       </c>
       <c r="E39" t="n">
-        <v>575</v>
+        <v>750</v>
       </c>
       <c r="F39" t="n">
-        <v>148</v>
+        <v>185</v>
       </c>
       <c r="G39" t="n">
-        <v>45</v>
+        <v>138</v>
       </c>
       <c r="H39" t="n">
-        <v>45</v>
+        <v>138</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -2649,16 +2649,16 @@
         <v>1880</v>
       </c>
       <c r="E40" t="n">
-        <v>590</v>
+        <v>770</v>
       </c>
       <c r="F40" t="n">
-        <v>152</v>
+        <v>190</v>
       </c>
       <c r="G40" t="n">
-        <v>46</v>
+        <v>143</v>
       </c>
       <c r="H40" t="n">
-        <v>46</v>
+        <v>143</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -2705,16 +2705,16 @@
         <v>1930</v>
       </c>
       <c r="E41" t="n">
-        <v>605</v>
+        <v>790</v>
       </c>
       <c r="F41" t="n">
-        <v>156</v>
+        <v>195</v>
       </c>
       <c r="G41" t="n">
-        <v>47</v>
+        <v>148</v>
       </c>
       <c r="H41" t="n">
-        <v>47</v>
+        <v>148</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -2761,16 +2761,16 @@
         <v>1980</v>
       </c>
       <c r="E42" t="n">
-        <v>620</v>
+        <v>810</v>
       </c>
       <c r="F42" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="G42" t="n">
-        <v>48</v>
+        <v>153</v>
       </c>
       <c r="H42" t="n">
-        <v>48</v>
+        <v>153</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -2817,16 +2817,16 @@
         <v>2030</v>
       </c>
       <c r="E43" t="n">
-        <v>635</v>
+        <v>830</v>
       </c>
       <c r="F43" t="n">
-        <v>164</v>
+        <v>205</v>
       </c>
       <c r="G43" t="n">
-        <v>49</v>
+        <v>158</v>
       </c>
       <c r="H43" t="n">
-        <v>49</v>
+        <v>158</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -2873,16 +2873,16 @@
         <v>2080</v>
       </c>
       <c r="E44" t="n">
-        <v>650</v>
+        <v>850</v>
       </c>
       <c r="F44" t="n">
-        <v>168</v>
+        <v>210</v>
       </c>
       <c r="G44" t="n">
-        <v>50</v>
+        <v>163</v>
       </c>
       <c r="H44" t="n">
-        <v>50</v>
+        <v>163</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -2929,16 +2929,16 @@
         <v>2130</v>
       </c>
       <c r="E45" t="n">
-        <v>665</v>
+        <v>870</v>
       </c>
       <c r="F45" t="n">
-        <v>172</v>
+        <v>215</v>
       </c>
       <c r="G45" t="n">
-        <v>51</v>
+        <v>168</v>
       </c>
       <c r="H45" t="n">
-        <v>51</v>
+        <v>168</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -2985,16 +2985,16 @@
         <v>2180</v>
       </c>
       <c r="E46" t="n">
-        <v>680</v>
+        <v>890</v>
       </c>
       <c r="F46" t="n">
-        <v>176</v>
+        <v>220</v>
       </c>
       <c r="G46" t="n">
-        <v>52</v>
+        <v>173</v>
       </c>
       <c r="H46" t="n">
-        <v>52</v>
+        <v>173</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -3041,16 +3041,16 @@
         <v>2230</v>
       </c>
       <c r="E47" t="n">
-        <v>695</v>
+        <v>910</v>
       </c>
       <c r="F47" t="n">
-        <v>180</v>
+        <v>225</v>
       </c>
       <c r="G47" t="n">
-        <v>53</v>
+        <v>178</v>
       </c>
       <c r="H47" t="n">
-        <v>53</v>
+        <v>178</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
@@ -3097,16 +3097,16 @@
         <v>2280</v>
       </c>
       <c r="E48" t="n">
-        <v>710</v>
+        <v>930</v>
       </c>
       <c r="F48" t="n">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="G48" t="n">
-        <v>54</v>
+        <v>183</v>
       </c>
       <c r="H48" t="n">
-        <v>54</v>
+        <v>183</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
@@ -3153,16 +3153,16 @@
         <v>2330</v>
       </c>
       <c r="E49" t="n">
-        <v>725</v>
+        <v>950</v>
       </c>
       <c r="F49" t="n">
+        <v>235</v>
+      </c>
+      <c r="G49" t="n">
         <v>188</v>
       </c>
-      <c r="G49" t="n">
-        <v>55</v>
-      </c>
       <c r="H49" t="n">
-        <v>55</v>
+        <v>188</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
@@ -3209,16 +3209,16 @@
         <v>2380</v>
       </c>
       <c r="E50" t="n">
-        <v>740</v>
+        <v>970</v>
       </c>
       <c r="F50" t="n">
-        <v>192</v>
+        <v>240</v>
       </c>
       <c r="G50" t="n">
-        <v>56</v>
+        <v>193</v>
       </c>
       <c r="H50" t="n">
-        <v>56</v>
+        <v>193</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
@@ -3265,16 +3265,16 @@
         <v>2430</v>
       </c>
       <c r="E51" t="n">
-        <v>755</v>
+        <v>990</v>
       </c>
       <c r="F51" t="n">
-        <v>196</v>
+        <v>245</v>
       </c>
       <c r="G51" t="n">
-        <v>57</v>
+        <v>198</v>
       </c>
       <c r="H51" t="n">
-        <v>57</v>
+        <v>198</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
@@ -3321,16 +3321,16 @@
         <v>2480</v>
       </c>
       <c r="E52" t="n">
-        <v>770</v>
+        <v>1010</v>
       </c>
       <c r="F52" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="G52" t="n">
-        <v>58</v>
+        <v>203</v>
       </c>
       <c r="H52" t="n">
-        <v>58</v>
+        <v>203</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
@@ -3377,16 +3377,16 @@
         <v>2530</v>
       </c>
       <c r="E53" t="n">
-        <v>785</v>
+        <v>1030</v>
       </c>
       <c r="F53" t="n">
-        <v>204</v>
+        <v>255</v>
       </c>
       <c r="G53" t="n">
-        <v>59</v>
+        <v>208</v>
       </c>
       <c r="H53" t="n">
-        <v>59</v>
+        <v>208</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
@@ -3433,16 +3433,16 @@
         <v>2580</v>
       </c>
       <c r="E54" t="n">
-        <v>800</v>
+        <v>1050</v>
       </c>
       <c r="F54" t="n">
-        <v>208</v>
+        <v>260</v>
       </c>
       <c r="G54" t="n">
-        <v>60</v>
+        <v>213</v>
       </c>
       <c r="H54" t="n">
-        <v>60</v>
+        <v>213</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
@@ -3489,16 +3489,16 @@
         <v>2630</v>
       </c>
       <c r="E55" t="n">
-        <v>815</v>
+        <v>1070</v>
       </c>
       <c r="F55" t="n">
-        <v>212</v>
+        <v>265</v>
       </c>
       <c r="G55" t="n">
-        <v>61</v>
+        <v>218</v>
       </c>
       <c r="H55" t="n">
-        <v>61</v>
+        <v>218</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
@@ -3545,16 +3545,16 @@
         <v>2680</v>
       </c>
       <c r="E56" t="n">
-        <v>830</v>
+        <v>1090</v>
       </c>
       <c r="F56" t="n">
-        <v>216</v>
+        <v>270</v>
       </c>
       <c r="G56" t="n">
-        <v>62</v>
+        <v>223</v>
       </c>
       <c r="H56" t="n">
-        <v>62</v>
+        <v>223</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
@@ -3601,16 +3601,16 @@
         <v>2730</v>
       </c>
       <c r="E57" t="n">
-        <v>845</v>
+        <v>1110</v>
       </c>
       <c r="F57" t="n">
-        <v>220</v>
+        <v>275</v>
       </c>
       <c r="G57" t="n">
-        <v>63</v>
+        <v>228</v>
       </c>
       <c r="H57" t="n">
-        <v>63</v>
+        <v>228</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
@@ -3657,16 +3657,16 @@
         <v>2780</v>
       </c>
       <c r="E58" t="n">
-        <v>860</v>
+        <v>1130</v>
       </c>
       <c r="F58" t="n">
-        <v>224</v>
+        <v>280</v>
       </c>
       <c r="G58" t="n">
-        <v>64</v>
+        <v>233</v>
       </c>
       <c r="H58" t="n">
-        <v>64</v>
+        <v>233</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>

--- a/Configs/GameConfig/Datas/HeroGrowthConfig.xlsx
+++ b/Configs/GameConfig/Datas/HeroGrowthConfig.xlsx
@@ -1,34 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Reba13a948af84f6b"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,12 +43,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -288,7 +283,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -297,13 +292,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -337,17 +332,6 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -402,223 +386,214 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:S58"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>##var</t>
+          <t xml:space="preserve">##var</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>HeroId</t>
+          <t xml:space="preserve">HeroId</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Level</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Stats</t>
-        </is>
+          <t xml:space="preserve">Level</t>
+        </is>
+      </c>
+      <c r="D1" t="str">
+        <v>BaseAttributes</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>##var</t>
+          <t xml:space="preserve">##var</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MaxHp</t>
+          <t xml:space="preserve">MaxHp</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MaxMp</t>
+          <t xml:space="preserve">MaxMp</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t xml:space="preserve">Power</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Def</t>
+          <t xml:space="preserve">Def</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Mdef</t>
+          <t xml:space="preserve">Mdef</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Crit</t>
+          <t xml:space="preserve">Crit</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t xml:space="preserve">Miss</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t xml:space="preserve">Lucky</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Toughness</t>
+          <t xml:space="preserve">Toughness</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Htarget</t>
+          <t xml:space="preserve">Htarget</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>CritReduce</t>
+          <t xml:space="preserve">CritReduce</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Ar</t>
+          <t xml:space="preserve">Ar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sp</t>
+          <t xml:space="preserve">Sp</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Vampirism</t>
+          <t xml:space="preserve">Vampirism</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>HpRegen</t>
+          <t xml:space="preserve">HpRegen</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>MpRegen</t>
+          <t xml:space="preserve">MpRegen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>##</t>
+          <t xml:space="preserve">##</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>英雄ID(对应 HeroConfig.Id)</t>
+          <t xml:space="preserve">英雄ID(对应 HeroConfig.Id)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>等级(1 起连续)</t>
+          <t xml:space="preserve">等级(1 起连续)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>生命上限</t>
+          <t xml:space="preserve">生命上限</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>魔法上限</t>
+          <t xml:space="preserve">魔法上限</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t xml:space="preserve">攻击</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>物防</t>
+          <t xml:space="preserve">物防</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>魔防</t>
+          <t xml:space="preserve">魔防</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>暴击</t>
+          <t xml:space="preserve">暴击</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>闪避</t>
+          <t xml:space="preserve">闪避</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>幸运(加暴击倍率)</t>
+          <t xml:space="preserve">幸运(加暴击倍率)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>韧性(减对方幸运)</t>
+          <t xml:space="preserve">韧性(减对方幸运)</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>命中(减对方闪避)</t>
+          <t xml:space="preserve">命中(减对方闪避)</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>暴击抵抗</t>
+          <t xml:space="preserve">暴击抵抗</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>破甲(减对方物防)</t>
+          <t xml:space="preserve">破甲(减对方物防)</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>破魔(减对方魔防)</t>
+          <t xml:space="preserve">破魔(减对方魔防)</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>吸血(百分点,伤害转生命)</t>
+          <t xml:space="preserve">吸血(百分点,伤害转生命)</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>每秒回血</t>
+          <t xml:space="preserve">每秒回血</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>每秒回蓝</t>
+          <t xml:space="preserve">每秒回蓝</t>
         </is>
       </c>
     </row>
@@ -642,7 +617,7 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -698,7 +673,7 @@
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -754,7 +729,7 @@
         <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -810,7 +785,7 @@
         <v>8</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -866,7 +841,7 @@
         <v>10</v>
       </c>
       <c r="H8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -922,7 +897,7 @@
         <v>12</v>
       </c>
       <c r="H9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -978,7 +953,7 @@
         <v>14</v>
       </c>
       <c r="H10" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1034,7 +1009,7 @@
         <v>16</v>
       </c>
       <c r="H11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1090,7 +1065,7 @@
         <v>18</v>
       </c>
       <c r="H12" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1146,7 +1121,7 @@
         <v>20</v>
       </c>
       <c r="H13" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1202,7 +1177,7 @@
         <v>22</v>
       </c>
       <c r="H14" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1258,7 +1233,7 @@
         <v>24</v>
       </c>
       <c r="H15" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1314,7 +1289,7 @@
         <v>26</v>
       </c>
       <c r="H16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1370,7 +1345,7 @@
         <v>28</v>
       </c>
       <c r="H17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1426,7 +1401,7 @@
         <v>33</v>
       </c>
       <c r="H18" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1482,7 +1457,7 @@
         <v>38</v>
       </c>
       <c r="H19" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1538,7 +1513,7 @@
         <v>43</v>
       </c>
       <c r="H20" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -1594,7 +1569,7 @@
         <v>48</v>
       </c>
       <c r="H21" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -1650,7 +1625,7 @@
         <v>53</v>
       </c>
       <c r="H22" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -1706,7 +1681,7 @@
         <v>58</v>
       </c>
       <c r="H23" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -1762,7 +1737,7 @@
         <v>63</v>
       </c>
       <c r="H24" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -1818,7 +1793,7 @@
         <v>68</v>
       </c>
       <c r="H25" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -1874,7 +1849,7 @@
         <v>73</v>
       </c>
       <c r="H26" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -1930,7 +1905,7 @@
         <v>78</v>
       </c>
       <c r="H27" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -1986,7 +1961,7 @@
         <v>83</v>
       </c>
       <c r="H28" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -2042,7 +2017,7 @@
         <v>88</v>
       </c>
       <c r="H29" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2098,7 +2073,7 @@
         <v>93</v>
       </c>
       <c r="H30" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2154,7 +2129,7 @@
         <v>98</v>
       </c>
       <c r="H31" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -2210,7 +2185,7 @@
         <v>103</v>
       </c>
       <c r="H32" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -2266,7 +2241,7 @@
         <v>108</v>
       </c>
       <c r="H33" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -2322,7 +2297,7 @@
         <v>113</v>
       </c>
       <c r="H34" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -2378,7 +2353,7 @@
         <v>118</v>
       </c>
       <c r="H35" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -2434,7 +2409,7 @@
         <v>123</v>
       </c>
       <c r="H36" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -2490,7 +2465,7 @@
         <v>128</v>
       </c>
       <c r="H37" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -2546,7 +2521,7 @@
         <v>133</v>
       </c>
       <c r="H38" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -2602,7 +2577,7 @@
         <v>138</v>
       </c>
       <c r="H39" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -2658,7 +2633,7 @@
         <v>143</v>
       </c>
       <c r="H40" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -2714,7 +2689,7 @@
         <v>148</v>
       </c>
       <c r="H41" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -2770,7 +2745,7 @@
         <v>153</v>
       </c>
       <c r="H42" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -2826,7 +2801,7 @@
         <v>158</v>
       </c>
       <c r="H43" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -2882,7 +2857,7 @@
         <v>163</v>
       </c>
       <c r="H44" t="n">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -2938,7 +2913,7 @@
         <v>168</v>
       </c>
       <c r="H45" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -2994,7 +2969,7 @@
         <v>173</v>
       </c>
       <c r="H46" t="n">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -3050,7 +3025,7 @@
         <v>178</v>
       </c>
       <c r="H47" t="n">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
@@ -3106,7 +3081,7 @@
         <v>183</v>
       </c>
       <c r="H48" t="n">
-        <v>183</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
@@ -3162,7 +3137,7 @@
         <v>188</v>
       </c>
       <c r="H49" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
@@ -3218,7 +3193,7 @@
         <v>193</v>
       </c>
       <c r="H50" t="n">
-        <v>193</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
@@ -3274,7 +3249,7 @@
         <v>198</v>
       </c>
       <c r="H51" t="n">
-        <v>198</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
@@ -3330,7 +3305,7 @@
         <v>203</v>
       </c>
       <c r="H52" t="n">
-        <v>203</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
@@ -3386,7 +3361,7 @@
         <v>208</v>
       </c>
       <c r="H53" t="n">
-        <v>208</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
@@ -3442,7 +3417,7 @@
         <v>213</v>
       </c>
       <c r="H54" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
@@ -3498,7 +3473,7 @@
         <v>218</v>
       </c>
       <c r="H55" t="n">
-        <v>218</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
@@ -3554,7 +3529,7 @@
         <v>223</v>
       </c>
       <c r="H56" t="n">
-        <v>223</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
@@ -3610,7 +3585,7 @@
         <v>228</v>
       </c>
       <c r="H57" t="n">
-        <v>228</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
@@ -3666,7 +3641,7 @@
         <v>233</v>
       </c>
       <c r="H58" t="n">
-        <v>233</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
@@ -3703,9 +3678,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells>
     <mergeCell ref="D1:S1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>